--- a/Table/Datas/SkillData.xlsx
+++ b/Table/Datas/SkillData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Study\Unreal\ProjectH\Table\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCE352DB-D357-49DE-80D0-3DD1825DBFED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36E70C5D-2A0D-4EF7-893E-301C436B7734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="34">
   <si>
     <t>!Field</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -153,6 +153,10 @@
   </si>
   <si>
     <t>Cerafina_Skill1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TargetCount</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -526,16 +530,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:H14"/>
+  <dimension ref="A2:I14"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="8" width="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15" customWidth="1"/>
+    <col min="5" max="9" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -560,8 +564,11 @@
       <c r="H2" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -586,8 +593,11 @@
       <c r="H3" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -598,22 +608,25 @@
         <v>14</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -624,22 +637,25 @@
         <v>14</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I5" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>1001</v>
       </c>
@@ -649,23 +665,26 @@
       <c r="C6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="3">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="3">
-        <v>1</v>
-      </c>
-      <c r="F6" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6" s="3">
-        <v>1</v>
+      <c r="F6" s="3">
+        <v>1</v>
+      </c>
+      <c r="G6" s="3" t="b">
+        <v>0</v>
       </c>
       <c r="H6" s="3">
+        <v>1</v>
+      </c>
+      <c r="I6" s="3">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>1002</v>
       </c>
@@ -675,23 +694,26 @@
       <c r="C7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="3">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="3">
+      <c r="F7" s="3">
         <v>1.5</v>
       </c>
-      <c r="F7" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7" s="3">
+      <c r="G7" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" s="3">
         <v>2</v>
       </c>
-      <c r="H7" s="3">
+      <c r="I7" s="3">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>1003</v>
       </c>
@@ -701,23 +723,26 @@
       <c r="C8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="3">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" s="3">
         <v>3</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>1004</v>
       </c>
@@ -727,23 +752,26 @@
       <c r="C9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="3">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="3">
-        <v>0</v>
-      </c>
-      <c r="F9" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G9" s="3">
-        <v>1</v>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3" t="b">
+        <v>0</v>
       </c>
       <c r="H9" s="3">
+        <v>1</v>
+      </c>
+      <c r="I9" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <v>2001</v>
       </c>
@@ -753,23 +781,26 @@
       <c r="C10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="3">
-        <v>1</v>
-      </c>
-      <c r="F10" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G10" s="3">
+      <c r="F10" s="3">
+        <v>1</v>
+      </c>
+      <c r="G10" s="3" t="b">
         <v>1</v>
       </c>
       <c r="H10" s="3">
+        <v>1</v>
+      </c>
+      <c r="I10" s="3">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>2002</v>
       </c>
@@ -779,23 +810,26 @@
       <c r="C11" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="3">
+        <v>3</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="3">
+      <c r="F11" s="3">
         <v>1.3</v>
       </c>
-      <c r="F11" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G11" s="3">
-        <v>1</v>
+      <c r="G11" s="3" t="b">
+        <v>0</v>
       </c>
       <c r="H11" s="3">
+        <v>1</v>
+      </c>
+      <c r="I11" s="3">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <v>2003</v>
       </c>
@@ -805,23 +839,26 @@
       <c r="C12" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="3">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E12" s="3">
-        <v>0</v>
-      </c>
-      <c r="F12" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G12" s="3">
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3" t="b">
         <v>1</v>
       </c>
       <c r="H12" s="3">
+        <v>1</v>
+      </c>
+      <c r="I12" s="3">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>2004</v>
       </c>
@@ -831,23 +868,26 @@
       <c r="C13" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="3">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E13" s="3">
-        <v>0</v>
-      </c>
-      <c r="F13" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G13" s="3">
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3" t="b">
         <v>1</v>
       </c>
       <c r="H13" s="3">
+        <v>1</v>
+      </c>
+      <c r="I13" s="3">
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>2005</v>
       </c>
@@ -857,19 +897,22 @@
       <c r="C14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="3">
-        <v>1</v>
-      </c>
-      <c r="F14" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="F14" s="3">
+        <v>1</v>
+      </c>
+      <c r="G14" s="3" t="b">
         <v>1</v>
       </c>
       <c r="H14" s="3">
+        <v>1</v>
+      </c>
+      <c r="I14" s="3">
         <v>0</v>
       </c>
     </row>

--- a/Table/Datas/SkillData.xlsx
+++ b/Table/Datas/SkillData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Study\Unreal\ProjectH\Table\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36E70C5D-2A0D-4EF7-893E-301C436B7734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B72865A5-918C-4FD3-AA50-D815218A58E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="34">
   <si>
     <t>!Field</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -530,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:I14"/>
+  <dimension ref="A2:I15"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
@@ -916,6 +916,35 @@
         <v>0</v>
       </c>
     </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="4">
+        <v>2006</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" s="3">
+        <v>1</v>
+      </c>
+      <c r="G15" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" s="3">
+        <v>1</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Table/Datas/SkillData.xlsx
+++ b/Table/Datas/SkillData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Study\Unreal\ProjectH\Table\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B72865A5-918C-4FD3-AA50-D815218A58E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94131820-834C-4F0A-A071-96468FE2FFDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="35">
   <si>
     <t>!Field</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -157,6 +157,10 @@
   </si>
   <si>
     <t>TargetCount</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffTableNo</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -530,16 +534,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:I15"/>
+  <dimension ref="A2:J15"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="15" customWidth="1"/>
-    <col min="5" max="9" width="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -567,8 +571,11 @@
       <c r="I2" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -596,8 +603,11 @@
       <c r="I3" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -625,8 +635,11 @@
       <c r="I4" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J4" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -654,8 +667,11 @@
       <c r="I5" s="2" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J5" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>1001</v>
       </c>
@@ -683,8 +699,11 @@
       <c r="I6" s="3">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J6" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>1002</v>
       </c>
@@ -712,8 +731,11 @@
       <c r="I7" s="3">
         <v>8</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J7" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>1003</v>
       </c>
@@ -741,8 +763,11 @@
       <c r="I8" s="3">
         <v>12</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>1004</v>
       </c>
@@ -770,8 +795,11 @@
       <c r="I9" s="3">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <v>2001</v>
       </c>
@@ -799,8 +827,11 @@
       <c r="I10" s="3">
         <v>7</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>2002</v>
       </c>
@@ -828,8 +859,11 @@
       <c r="I11" s="3">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J11" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <v>2003</v>
       </c>
@@ -857,8 +891,11 @@
       <c r="I12" s="3">
         <v>7</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J12" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>2004</v>
       </c>
@@ -886,8 +923,11 @@
       <c r="I13" s="3">
         <v>7</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>2005</v>
       </c>
@@ -915,8 +955,11 @@
       <c r="I14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J14" s="3">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>2006</v>
       </c>
@@ -942,6 +985,9 @@
         <v>1</v>
       </c>
       <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
         <v>0</v>
       </c>
     </row>

--- a/Table/Datas/SkillData.xlsx
+++ b/Table/Datas/SkillData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Study\Unreal\ProjectH\Table\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94131820-834C-4F0A-A071-96468FE2FFDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2374E58-DECC-4CC1-A7D8-4009266F98D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-27435" yWindow="2085" windowWidth="21600" windowHeight="12570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -988,7 +988,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>1001</v>
       </c>
     </row>
   </sheetData>

--- a/Table/Datas/SkillData.xlsx
+++ b/Table/Datas/SkillData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Study\Unreal\ProjectH\Table\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2374E58-DECC-4CC1-A7D8-4009266F98D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2A9FA2D-7FAA-455F-A1A2-A548319C6A8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27435" yWindow="2085" windowWidth="21600" windowHeight="12570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2850" yWindow="1320" windowWidth="23745" windowHeight="13080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -988,7 +988,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="3">
-        <v>1001</v>
+        <v>1002</v>
       </c>
     </row>
   </sheetData>

--- a/Table/Datas/SkillData.xlsx
+++ b/Table/Datas/SkillData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Study\Unreal\ProjectH\Table\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2A9FA2D-7FAA-455F-A1A2-A548319C6A8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DEB5160-D561-40CA-B8BC-920FC7A84C03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2850" yWindow="1320" windowWidth="23745" windowHeight="13080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="60" yWindow="720" windowWidth="23745" windowHeight="13080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="39">
   <si>
     <t>!Field</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -160,7 +160,23 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>BuffTableNo</t>
+    <t>Value</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillValueType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DeBuff</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -534,16 +550,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:J15"/>
+  <dimension ref="A2:K15"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="15" customWidth="1"/>
-    <col min="5" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="11" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -574,8 +590,11 @@
       <c r="J2" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -606,8 +625,11 @@
       <c r="J3" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -636,10 +658,13 @@
         <v>31</v>
       </c>
       <c r="J4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -668,10 +693,13 @@
         <v>30</v>
       </c>
       <c r="J5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>1001</v>
       </c>
@@ -699,11 +727,14 @@
       <c r="I6" s="3">
         <v>6</v>
       </c>
-      <c r="J6" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="K6" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>1002</v>
       </c>
@@ -731,11 +762,14 @@
       <c r="I7" s="3">
         <v>8</v>
       </c>
-      <c r="J7" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="K7" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>1003</v>
       </c>
@@ -763,11 +797,14 @@
       <c r="I8" s="3">
         <v>12</v>
       </c>
-      <c r="J8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="K8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>1004</v>
       </c>
@@ -795,11 +832,14 @@
       <c r="I9" s="3">
         <v>10</v>
       </c>
-      <c r="J9" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J9" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="K9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <v>2001</v>
       </c>
@@ -827,11 +867,14 @@
       <c r="I10" s="3">
         <v>7</v>
       </c>
-      <c r="J10" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J10" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="K10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>2002</v>
       </c>
@@ -859,11 +902,14 @@
       <c r="I11" s="3">
         <v>9</v>
       </c>
-      <c r="J11" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J11" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="K11" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <v>2003</v>
       </c>
@@ -891,11 +937,14 @@
       <c r="I12" s="3">
         <v>7</v>
       </c>
-      <c r="J12" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J12" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="K12" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>2004</v>
       </c>
@@ -923,11 +972,14 @@
       <c r="I13" s="3">
         <v>7</v>
       </c>
-      <c r="J13" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J13" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="K13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>2005</v>
       </c>
@@ -955,11 +1007,14 @@
       <c r="I14" s="3">
         <v>0</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K14" s="3">
         <v>1001</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>2006</v>
       </c>
@@ -987,7 +1042,10 @@
       <c r="I15" s="3">
         <v>0</v>
       </c>
-      <c r="J15" s="3">
+      <c r="J15" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K15" s="3">
         <v>1002</v>
       </c>
     </row>
